--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -721,8 +721,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>30.67</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -778,8 +782,12 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -3693,8 +3701,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>30.67</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -3750,8 +3762,12 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -8093,8 +8109,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="H35" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>30.67</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -8150,8 +8170,12 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+      <c r="U35" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -9247,8 +9271,12 @@
           <t>1.70 ~ 2.10</t>
         </is>
       </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="H40" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>49.28</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -9304,8 +9332,12 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
+      <c r="U40" s="4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>2.79</v>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -9532,7 +9564,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U41" s="3"/>
+      <c r="U41" s="4" t="n">
+        <v>4.37</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
@@ -10141,8 +10175,12 @@
           <t>1.60 ~ 2.00</t>
         </is>
       </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="H44" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>39.28</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -10186,8 +10224,12 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
+      <c r="U44" s="4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>2.54</v>
+      </c>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
@@ -10297,9 +10339,7 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ44" s="4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="AZ44" s="3"/>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
@@ -11247,8 +11287,12 @@
           <t>1.47 ~ 1.67</t>
         </is>
       </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="H49" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>32.67</v>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -11304,8 +11348,12 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
+      <c r="U49" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -14985,8 +15033,12 @@
           <t>1.50 ~ 1.73</t>
         </is>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="H65" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>49.39</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -16898,7 +16950,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U73" s="3"/>
+      <c r="U73" s="4" t="n">
+        <v>3.38</v>
+      </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
@@ -17364,7 +17418,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U75" s="3"/>
+      <c r="U75" s="4" t="n">
+        <v>3.36</v>
+      </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -7182,7 +7182,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26桐投01</t>
+          <t>26之江城投PPN001B</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7190,64 +7190,60 @@
           <t>08-25 18:00</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>283633.SH</t>
-        </is>
-      </c>
+      <c r="C31" s="3"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>70.28</v>
+        <v>50.28</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24桐投02</t>
+          <t>26之江03</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>3.20Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7567</t>
+          <t>1.8671</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>桐庐县城市建设投资集团有限公司</t>
+          <t>杭州之江城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>D- 0.80</t>
+          <t>B- 49.60</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7270,21 +7266,23 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4" t="n">
+        <v>4.58</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
@@ -7295,18 +7293,18 @@
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券的发行总额不超过6.00亿元，一次发行。根据发行人的财务状况和资金需求情况，本期债券募集资金扣除发行费用后，募集资金拟全部仅用于偿还到期的公司债券本金[23 桐投01]</t>
+          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,财通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7316,12 +7314,12 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>桐庐县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7337,7 +7335,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7352,7 +7350,7 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
@@ -7367,12 +7365,12 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
@@ -7410,7 +7408,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26之江城投PPN001B</t>
+          <t>26凉旅投资PPN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7425,53 +7423,49 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>50.28</v>
-      </c>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26之江03</t>
+          <t>26凉旅01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>4.43Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8671</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司</t>
+          <t>凉山州文旅投资发展集团有限责任公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 49.60</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7481,7 +7475,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7494,39 +7488,37 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U32" s="4" t="n">
-        <v>4.58</v>
-      </c>
+      <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>2.50%~2.60%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>四川省-凉山彝族自治州</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
+          <t>本次定向债务融资工具注册金额为7亿元,首期发行金额为人民7亿元。募集资金用于偿还到期有息债务。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
+          <t>东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7547,7 +7539,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种二)</t>
+          <t>凉山州文旅投资发展集团有限责任公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7578,32 +7570,28 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3"/>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>消费者服务</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合消费者服务</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合消费者服务</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>酒店</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7636,7 +7624,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26凉旅投资PPN001</t>
+          <t>26之江城投PPN001A</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7647,106 +7635,114 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>36.28</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>24之江03</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>2.82Y</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>1.6945</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/1.7500</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>杭州之江城市建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>B- 49.60</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>08-25 15:00</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>26凉旅01</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>4.43Y</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>1.8952</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>凉山州文旅投资发展集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>08-25 09:00</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+      <c r="U33" s="4" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>11.5</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.50%~2.60%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-凉山彝族自治州</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册金额为7亿元,首期发行金额为人民7亿元。募集资金用于偿还到期有息债务。</t>
+          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7767,7 +7763,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>凉山州文旅投资发展集团有限责任公司2026年度第一期定向债务融资工具</t>
+          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7798,33 +7794,37 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>消费者服务</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>酒店</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7852,7 +7852,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26之江城投PPN001A</t>
+          <t>26铁塔股份MTN003</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7860,60 +7860,66 @@
           <t>08-25 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>102683364.IB</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>40.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>40.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>36.28</v>
+        <v>30.67</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24之江03</t>
+          <t>26铁塔股份MTN001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.82Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6945</t>
+          <t>1.6451</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/1.7500</t>
+          <t>1.6600/1.6400</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司</t>
+          <t>中国铁塔股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 49.60</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7923,7 +7929,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7937,19 +7943,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>4.56</v>
+        <v>1.86</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>11.5</v>
+        <v>1.0</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7960,28 +7966,28 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
+          <t>本期中期票据发行金额40亿元,募集资金24.6亿元拟将用于偿还有息债务,15.4亿元拟将用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
+          <t>中国银行股份有限公司,中国农业银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -7991,20 +7997,24 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种一)</t>
+          <t>中国铁塔股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -8022,37 +8032,37 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子设备制造</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV34" s="3" t="inlineStr">
@@ -8062,7 +8072,7 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
@@ -8080,49 +8090,45 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26铁塔股份MTN003</t>
+          <t>26威高MTN003(科创债)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683364.IB</t>
+          <t>102683369.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>40.0</v>
+        <v>5.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>40.0</v>
+        <v>5.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>30.67</v>
-      </c>
+          <t>2.40 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26铁塔股份MTN001</t>
+          <t>26威高MTN002(科创债)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -8132,22 +8138,22 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6451</t>
+          <t>2.7328</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6400</t>
+          <t>--/2.7000</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中国铁塔股份有限公司</t>
+          <t>威高集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>D- 2.00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8167,44 +8173,40 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>3.10%~3.20%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额40亿元,募集资金24.6亿元拟将用于偿还有息债务,15.4亿元拟将用于补充流动资金。</t>
+          <t>本次中期票据发行规模不超过人民币5亿元,用途为偿还有息债务</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国农业银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8215,7 +8217,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8225,7 +8227,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中国铁塔股份有限公司2026年度第三期中期票据</t>
+          <t>威高集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8235,82 +8237,78 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>医药制造</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>医疗器械制造</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>医疗器械制造</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>医疗器械</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY35" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>电子设备制造</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>通信设备</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>通信设备</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>通信设备</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AZ35" s="3"/>
@@ -8318,70 +8316,72 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26威高MTN003(科创债)</t>
+          <t>26蓉高04</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683369.IB</t>
+          <t>245886.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>6.85</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26威高MTN002(科创债)</t>
+          <t>26蓉高03</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>4.91Y+5.00Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.7328</t>
+          <t>1.7882</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/2.7000</t>
+          <t>1.8300/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>威高集团有限公司</t>
+          <t>成都高新投资集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>D- 2.00</t>
+          <t>C+ 34.90</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8401,61 +8401,63 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U36" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>7.13</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>3.10%~3.20%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行规模不超过人民币5亿元,用途为偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券21蓉高03的本金。[21蓉高03]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>威高集团有限公司2026年度第三期科技创新债券</t>
+          <t>成都高新投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8465,13 +8467,13 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2036-08-26</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8481,7 +8483,7 @@
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
@@ -8491,32 +8493,32 @@
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>医疗器械制造</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>医疗器械制造</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8526,7 +8528,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8536,7 +8538,7 @@
       </c>
       <c r="AY36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AZ36" s="3"/>
@@ -8544,72 +8546,74 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26蓉高04</t>
+          <t>26北部湾银行02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>245886.SH</t>
+          <t>2620006.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>30.0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>6.85</v>
+        <v>39.67</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26蓉高03</t>
+          <t>26北部湾银行01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.91Y+5.00Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7882</t>
+          <t>1.6468</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.8300/--</t>
+          <t>--/1.6400</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>成都高新投资集团有限公司</t>
+          <t>广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.90</t>
+          <t>B- 39.15</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8619,7 +8623,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8629,21 +8633,19 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>7.13</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8651,26 +8653,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券21蓉高03的本金。[21蓉高03]</t>
+          <t>本期债券募集资金将严格遵循法律法规及监管批复要求，专项用于补充本行投放向海经济领域信贷业务所需的资金，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,国海证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8680,12 +8686,12 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>成都高新投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>广西北部湾银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8695,7 +8701,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2036-08-26</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8711,42 +8717,42 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8756,7 +8762,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8774,74 +8780,74 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26北部湾银行02</t>
+          <t>26新希望MTN003(科创债)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 19:30</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>2620006.IB</t>
+          <t>102683344.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.90 ~ 2.50</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>39.67</v>
+        <v>96.39</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26北部湾银行01</t>
+          <t>26新希望MTN002(科创债)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>1.79Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6468</t>
+          <t>2.2020</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/1.6400</t>
+          <t>--/2.1800</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司</t>
+          <t>新希望集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 39.15</t>
+          <t>C- 20.52</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8861,19 +8867,19 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8881,35 +8887,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将严格遵循法律法规及监管批复要求，专项用于补充本行投放向海经济领域信贷业务所需的资金，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债务融资工具发行规模5亿元，拟用于偿还发行人下属子公司的有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,国海证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8919,7 +8921,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司2026年金融债券(第二期)</t>
+          <t>新希望集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8929,13 +8931,17 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2028-08-26</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
@@ -8945,37 +8951,37 @@
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>饲料</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9008,74 +9014,74 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26新希望MTN003(科创债)</t>
+          <t>26华能水电GN012</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:30</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102683344.IB</t>
+          <t>132680089.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.50</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>96.39</v>
+        <v>49.28</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26新希望MTN002(科创债)</t>
+          <t>26华能水电GN010</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>1.79Y</t>
+          <t>4.88Y+N</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.2020</t>
+          <t>1.8930</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/2.1800</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>新希望集团有限公司</t>
+          <t>华能澜沧江水电股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 20.52</t>
+          <t>C- 18.61</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9098,16 +9104,20 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>2.79</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9118,17 +9128,17 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模5亿元，拟用于偿还发行人下属子公司的有息债务</t>
+          <t>本期绿色中期票据拟发行金额10亿元,募集资金将用于偿还26华能水电GN005(乡村振兴)的本金。本期募集资金穿透后用于景洪水电站、糯扎渡水电站、黄登水电站、漫湾水电站等4个绿色项目[26华能水电GN005(乡村振兴)]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,天津银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9139,7 +9149,7 @@
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -9149,7 +9159,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>新希望集团有限公司2026年度第三期科技创新债券</t>
+          <t>华能澜沧江水电股份有限公司2026年度第十二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9159,14 +9169,10 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -9189,27 +9195,27 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9224,12 +9230,12 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY39" s="3" t="inlineStr">
@@ -9242,74 +9248,72 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN012</t>
+          <t>26化学K3</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>132680089.IB</t>
+          <t>245897.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>49.28</v>
+        <v>32.67</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN010</t>
+          <t>26化学K1</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.88Y+N</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8930</t>
+          <t>1.6442</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司</t>
+          <t>中国化学工程集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 18.61</t>
+          <t>C- 22.39</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9319,7 +9323,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9329,65 +9333,63 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>2.79</v>
-      </c>
+        <v>4.37</v>
+      </c>
+      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t>1.85%~1.95%</t>
-        </is>
-      </c>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X40" s="3"/>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z40" s="3"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据拟发行金额10亿元,募集资金将用于偿还26华能水电GN005(乡村振兴)的本金。本期募集资金穿透后用于景洪水电站、糯扎渡水电站、黄登水电站、漫湾水电站等4个绿色项目[26华能水电GN005(乡村振兴)]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司2026年度第十二期绿色中期票据</t>
+          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9397,25 +9399,25 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -9423,27 +9425,27 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9458,12 +9460,12 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY40" s="3" t="inlineStr">
@@ -9476,72 +9478,60 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26化学K3</t>
+          <t>26铁投02</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 00:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>245897.SH</t>
+          <t>283819.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>7.5</v>
+        <v>6.0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>32.67</v>
-      </c>
+          <t>2.90 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>26化学K1</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>2.81Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6442</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司</t>
+          <t>菏泽市铁路投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 22.39</t>
+          <t>C- 13.34</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9551,7 +9541,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 00:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9561,42 +9551,36 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U41" s="4" t="n">
-        <v>4.37</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X41" s="3"/>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
+          <t>本期债券募集资金不超过6.00亿元,募集资金扣除发行费用后,全部用于偿还公司债券本金[25铁投07]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>首创证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9607,7 +9591,7 @@
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
@@ -9617,20 +9601,24 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>菏泽市铁路投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
-        </is>
-      </c>
-      <c r="AK41" s="3"/>
+          <t>2033-08-28</t>
+        </is>
+      </c>
+      <c r="AK41" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9643,37 +9631,37 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9706,22 +9694,22 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26铁投02</t>
+          <t>26桐投01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>08-25 00:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283819.SH</t>
+          <t>283633.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -9730,56 +9718,68 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.90 ~ 3.50</t>
-        </is>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>70.28</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>24桐投02</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>3.20Y</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1.7567</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>桐庐县城市建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>D- 0.80</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>08-25 15:00</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>菏泽市铁路投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>C- 13.34</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>08-25 00:00</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="U42" s="3"/>
@@ -9789,26 +9789,30 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X42" s="3"/>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.96%~2.06%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过6.00亿元,募集资金扣除发行费用后,全部用于偿还公司债券本金[25铁投07]</t>
+          <t>本期债券的发行总额不超过6.00亿元，一次发行。根据发行人的财务状况和资金需求情况，本期债券募集资金扣除发行费用后，募集资金拟全部仅用于偿还到期的公司债券本金[23 桐投01]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>首创证券股份有限公司</t>
+          <t>国金证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9829,7 +9833,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>菏泽市铁路投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>桐庐县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9839,14 +9843,10 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2033-08-28</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9854,17 +9854,17 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -2296,7 +2296,7 @@
         <v>4.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>4.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26厦门国际银行永续债01</t>
+          <t>26南电SCP015</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9930,56 +9930,66 @@
           <t>08-25 18:00</t>
         </is>
       </c>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>012682150.IB</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.38Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>25.0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.20 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>19.11</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>22厦门国际银行永续债01</t>
+          <t>24南电GN001(碳中和债)</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>148D+N</t>
+          <t>165D</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.5901</t>
+          <t>1.4906</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.5900/1.5800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>厦门国际银行股份有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>A 79.69</t>
+          <t>B- 41.49</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9999,19 +10009,21 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U43" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>1.38</v>
+      </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -10019,35 +10031,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
+          <t>本期超短期融资券发行规模25亿元，募集资金用于补充发行人及下属单位营运资金。</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,华金证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,国开证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,光大证券股份有限公司,华夏银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
@@ -10057,7 +10065,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>厦门国际银行股份有限公司2026年无固定期限资本债券(第一期)</t>
+          <t>中国南方电网有限责任公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10067,60 +10075,60 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AO43" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ43" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR43" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10128,12 +10136,12 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY43" s="3" t="inlineStr">
@@ -10141,12 +10149,14 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ43" s="3"/>
+      <c r="AZ43" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26瑞士银行债01BC</t>
+          <t>26厦门国际银行永续债01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10154,106 +10164,124 @@
           <t>08-25 18:00</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>292680028.IB</t>
-        </is>
-      </c>
+      <c r="C44" s="3"/>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>30.0</v>
+      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>39.28</v>
-      </c>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>22厦门国际银行永续债01</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>148D+N</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1.5901</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>1.5900/1.5800</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>厦门国际银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>A 79.69</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>瑞士银行有限公司</t>
-        </is>
-      </c>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>08-25 09:00</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U44" s="4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.97%</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>福建省-厦门市</t>
+        </is>
+      </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金净额将由发行人用于其一般公司用途或满足瑞士银行有限公司(包括其分支机构)和其子公司的一般融资需求。预计不超过30%的募集资金净额将用于境内业务,剩余部分预计将由发行人以离岸人民币的形式汇往境外。</t>
+          <t>本期债券募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,瑞银证券有限责任公司,中国银行股份有限公司,中信银行股份有限公司,中国建设银行股份有限公司,中信证券股份有限公司,星展银行(中国)有限公司,第一创业证券承销保荐有限责任公司,富邦华一银行有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,平安银行股份有限公司,上海浦东发展银行股份有限公司,渣打银行(中国)有限公司,三井住友银行(中国)有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,华金证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,国开证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,光大证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -10263,7 +10291,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>瑞士银行有限公司2026年第一期人民币债券(债券通)</t>
+          <t>厦门国际银行股份有限公司2026年无固定期限资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10297,7 +10325,11 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP44" s="3"/>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -10310,10 +10342,14 @@
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>其他银行</t>
-        </is>
-      </c>
-      <c r="AT44" s="3"/>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10326,12 +10362,12 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY44" s="3" t="inlineStr">
@@ -10344,57 +10380,51 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26同安05</t>
+          <t>26瑞士银行债01BC</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>283709.SH</t>
+          <t>292680028.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.00</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>41.67</v>
+        <v>39.28</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>26同安04</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7484</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10404,14 +10434,10 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>同安控股有限责任公司</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>B 50.51</t>
-        </is>
-      </c>
+          <t>瑞士银行有限公司</t>
+        </is>
+      </c>
+      <c r="P45" s="3"/>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>2026-08-25</t>
@@ -10419,7 +10445,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10432,64 +10458,56 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
+      <c r="U45" s="4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>2.54</v>
+      </c>
       <c r="W45" s="3"/>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>1.78%~1.88%</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
-      <c r="AA45" s="3" t="inlineStr">
-        <is>
-          <t>安徽省-安庆市</t>
-        </is>
-      </c>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金。[23 同安04]</t>
+          <t>本期债券的募集资金净额将由发行人用于其一般公司用途或满足瑞士银行有限公司(包括其分支机构)和其子公司的一般融资需求。预计不超过30%的募集资金净额将用于境内业务,剩余部分预计将由发行人以离岸人民币的形式汇往境外。</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华安证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,瑞银证券有限责任公司,中国银行股份有限公司,中信银行股份有限公司,中国建设银行股份有限公司,中信证券股份有限公司,星展银行(中国)有限公司,第一创业证券承销保荐有限责任公司,富邦华一银行有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,平安银行股份有限公司,上海浦东发展银行股份有限公司,渣打银行(中国)有限公司,三井住友银行(中国)有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>同安控股有限责任公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
+          <t>瑞士银行有限公司2026年第一期人民币债券(债券通)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10500,7 +10518,7 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10510,34 +10528,26 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP45" s="3"/>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>纺织制造</t>
-        </is>
-      </c>
+          <t>其他银行</t>
+        </is>
+      </c>
+      <c r="AT45" s="3"/>
       <c r="AU45" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10568,59 +10578,57 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26南电SCP015</t>
+          <t>26同安05</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>012682150.IB</t>
+          <t>283709.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.38Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>25.0</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.50</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19.11</v>
+        <v>41.67</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24南电GN001(碳中和债)</t>
+          <t>26同安04</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>165D</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.4906</t>
+          <t>1.7484</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -10630,12 +10638,12 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>同安控股有限责任公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B- 41.49</t>
+          <t>B 50.51</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10645,7 +10653,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10655,117 +10663,113 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="W46" s="3"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-安庆市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模25亿元，募集资金用于补充发行人及下属单位营运资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金。[23 同安04]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,华安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第十五期超短期融资券</t>
+          <t>同安控股有限责任公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>纺织制造</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10793,9 +10797,7 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ46" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ46" s="3"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
@@ -17820,7 +17822,7 @@
         <v>6.0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -20564,7 +20566,7 @@
         <v>6.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -2075,7 +2075,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.8350/1.8350</t>
+          <t>1.8350/1.8325</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -10073,7 +10073,9 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AZ44" s="3"/>
+      <c r="AZ44" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
@@ -10293,7 +10295,9 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
@@ -12817,7 +12821,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>2.1500/2.1200</t>
+          <t>2.1400/2.1200</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -13485,7 +13489,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>2.3500/2.3200</t>
+          <t>2.3400/2.3200</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -4985,7 +4985,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.7200/1.7000</t>
+          <t>1.7150/1.7000</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7200/1.7000</t>
+          <t>1.7150/1.7000</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>2.0300/2.0000</t>
+          <t>2.0200/2.0000</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,11 @@
           <t>海南海峡航运股份有限公司</t>
         </is>
       </c>
-      <c r="P3" s="3"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -966,7 +970,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.8361</t>
+          <t>1.8320</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1445,7 +1449,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.07</t>
+          <t>C 28.70</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 38.62</t>
+          <t>B- 35.61</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1907,7 +1911,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 45.54</t>
+          <t>B- 44.10</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 24.44</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2373,7 +2377,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 17.19</t>
+          <t>C- 19.66</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2785,7 +2789,9 @@
       <c r="E12" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.80</t>
@@ -2829,7 +2835,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 39.62</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2852,7 +2858,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>2.7167</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -3059,7 +3067,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.39</t>
+          <t>C 28.94</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3295,7 +3303,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 40.64</t>
+          <t>B- 39.52</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3562,7 +3570,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
@@ -3753,7 +3761,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 48.63</t>
+          <t>B- 47.16</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3981,7 +3989,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 18.60</t>
+          <t>C 29.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4205,7 +4213,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 38.37</t>
+          <t>B- 38.35</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4437,7 +4445,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 39.00</t>
+          <t>B- 35.64</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4621,7 +4629,9 @@
       <c r="E20" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.80</t>
@@ -4665,7 +4675,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 46.23</t>
+          <t>B- 37.96</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4688,7 +4698,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>3.96</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -5361,7 +5373,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C 27.20</t>
+          <t>C 29.80</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5827,7 +5839,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.96</t>
+          <t>D+ 7.47</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6055,7 +6067,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.96</t>
+          <t>D+ 7.47</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6283,7 +6295,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.34</t>
+          <t>C+ 33.94</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6515,7 +6527,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.34</t>
+          <t>C+ 33.94</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6751,7 +6763,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 27.68</t>
+          <t>C 27.41</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6981,7 +6993,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 27.68</t>
+          <t>C 27.41</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7209,7 +7221,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 46.76</t>
+          <t>B- 47.95</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7441,7 +7453,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 20.45</t>
+          <t>C- 24.41</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7675,7 +7687,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 20.45</t>
+          <t>C- 24.41</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7863,7 +7875,9 @@
       <c r="E34" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>1.60 ~ 2.60</t>
@@ -7907,7 +7921,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.44</t>
+          <t>C- 24.20</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7930,7 +7944,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>2.74</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
@@ -8131,7 +8147,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 23.42</t>
+          <t>C+ 33.95</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8290,7 +8306,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26水发02</t>
+          <t>26麒麟02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8300,47 +8316,49 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>283824.SH</t>
+          <t>283782.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>2.50 ~ 3.50</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2.12</v>
+        <v>2.96</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>72.16</v>
+        <v>169.61</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26水发01</t>
+          <t>24阜阳债</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.67Y+2.00Y</t>
+          <t>2.65Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.1520</t>
+          <t>2.0002</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8350,12 +8368,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>水发集团有限公司</t>
+          <t>曲靖市麒麟区城乡建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.58</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8378,33 +8396,39 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U36" s="3"/>
+      <c r="U36" s="4" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>2.56%~2.66%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>云南省-曲靖市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[21水发02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还到期的公司债券本金[23 麒麟债]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,兴业证券股份有限公司,广发证券股份有限公司,德邦证券股份有限公司</t>
+          <t>太平洋证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8425,7 +8449,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>水发集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>曲靖市麒麟区城乡建设投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8435,7 +8459,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8456,27 +8480,27 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
@@ -8486,7 +8510,7 @@
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8496,7 +8520,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8514,7 +8538,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26麒麟02</t>
+          <t>26港航04</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8524,7 +8548,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>283782.SH</t>
+          <t>283726.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -8533,55 +8557,53 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.50</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>169.61</v>
+        <v>47.61</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>24阜阳债</t>
+          <t>26港航03</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.65Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.0002</t>
+          <t>1.7354</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/1.7450</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区城乡建设投资(集团)有限公司</t>
+          <t>苏州市港航投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 16.67</t>
+          <t>C+ 31.75</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8601,42 +8623,40 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>1.87</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>2.56%~2.66%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>云南省-曲靖市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还到期的公司债券本金[23 麒麟债]</t>
+          <t>本期公司债券募集资金7亿元扣除发行费用后,全部用于偿还到期的公司债券本金[23苏发02]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>太平洋证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8657,7 +8677,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区城乡建设投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>苏州市港航投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8667,7 +8687,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8683,37 +8703,37 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8746,7 +8766,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26港航04</t>
+          <t>26港航05</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8756,12 +8776,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283726.SH</t>
+          <t>283727.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -8770,18 +8790,18 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>47.61</v>
+        <v>49.16</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -8811,7 +8831,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 24.97</t>
+          <t>C+ 31.75</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8843,7 +8863,7 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8885,7 +8905,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>苏州市港航投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种一)</t>
+          <t>苏州市港航投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8895,7 +8915,7 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -8974,17 +8994,17 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26港航05</t>
+          <t>26盐城东方MTN001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>08-26 19:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>283727.SH</t>
+          <t>102683403.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -8993,112 +9013,118 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>65.16</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>25盐投05</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>3.58Y</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>1.8491</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>盐城东方投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>C- 14.99</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>08-26 09:00</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>3.4783</v>
+      </c>
+      <c r="V39" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>26港航03</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>2.84Y</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>1.7354</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>1.7700/1.7450</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>苏州市港航投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>C- 24.97</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>08-26 15:00</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金7亿元扣除发行费用后,全部用于偿还到期的公司债券本金[23苏发02]</t>
+          <t>发行人本次发行中期票据2.30亿元,所募集资金用于偿还发行人本部存量债务融资工具本金[23盐城东方PPN001]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9108,28 +9134,28 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>苏州市港航投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
+          <t>盐城东方投资开发集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9139,7 +9165,7 @@
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
@@ -9149,27 +9175,27 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9202,7 +9228,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26盐城东方MTN001</t>
+          <t>26中铁建金租债01</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9212,49 +9238,41 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683403.IB</t>
+          <t>2622018.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.3</v>
+        <v>10.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2.3</v>
+        <v>10.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>65.16</v>
+        <v>38.61</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>25盐投05</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>3.58Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8491</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9264,14 +9282,10 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>盐城东方投资开发集团有限公司</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>C- 15.92</t>
-        </is>
-      </c>
+          <t>中铁建金融租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P40" s="3"/>
       <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -9289,55 +9303,57 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.4783</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>3.5</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z40" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行中期票据2.30亿元,所募集资金用于偿还发行人本部存量债务融资工具本金[23盐城东方PPN001]</t>
+          <t>本期债券募集资金拟全部用于偿还到期债务，补充公司中长期资金来源</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,中国民生银行股份有限公司,兴业银行股份有限公司,招商银行股份有限公司,渤海银行股份有限公司,东方证券股份有限公司,中泰证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>其他金融债</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -9347,7 +9363,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>盐城东方投资开发集团有限公司2026年度第一期中期票据</t>
+          <t>中铁建金融租赁有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9357,53 +9373,53 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9436,7 +9452,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26中铁建金租债01</t>
+          <t>26国网租赁CP008</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9446,86 +9462,100 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2622018.IB</t>
+          <t>042680301.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.83Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>38.61</v>
+        <v>37.62</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>25国网租赁MTN003</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>294D</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>1.5900/--</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>国网国际融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>B- 42.25</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>08-26 09:00</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>中铁建金融租赁有限公司</t>
-        </is>
-      </c>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>08-26 09:00</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V41" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>1.3</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9533,11 +9563,7 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>天津市</t>
@@ -9545,18 +9571,18 @@
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还到期债务，补充公司中长期资金来源</t>
+          <t>本期短期融资券发行规模5亿元,全部用于偿还存量债务融资工具[25 国网租赁CP012( 绿色)]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,中国民生银行股份有限公司,兴业银行股份有限公司,招商银行股份有限公司,渤海银行股份有限公司,东方证券股份有限公司,中泰证券股份有限公司,国信证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>其他金融债</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9571,7 +9597,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>中铁建金融租赁有限公司2026年第一期金融债券</t>
+          <t>国网国际融资租赁有限公司2026年度第八期短期融资券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9581,23 +9607,23 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
@@ -9607,7 +9633,7 @@
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
@@ -9617,12 +9643,12 @@
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
@@ -9660,7 +9686,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26国网租赁CP008</t>
+          <t>26兴化城投PPN008</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9670,64 +9696,64 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>042680301.IB</t>
+          <t>032680494.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>0.83Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5.0</v>
+        <v>2.3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5.0</v>
+        <v>2.3</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>37.62</v>
+        <v>44.95</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25国网租赁MTN003</t>
+          <t>26兴化城投PPN006</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>294D</t>
+          <t>1.97Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.7283</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>国网国际融资租赁有限公司</t>
+          <t>兴化市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 45.40</t>
+          <t>C- 15.32</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9751,51 +9777,49 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>1.3</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行规模5亿元,全部用于偿还存量债务融资工具[25 国网租赁CP012( 绿色)]</t>
+          <t>本期定向债务融资工具发行金额2.3亿元,拟用于偿还发行人有息债务[26兴化城投SCP001]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
@@ -9805,20 +9829,24 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>国网国际融资租赁有限公司2026年度第八期短期融资券</t>
+          <t>兴化市城市建设投资有限公司2026年度第八期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK42" s="3"/>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="AK42" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -9836,32 +9864,32 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>农产品加工</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9894,7 +9922,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN008</t>
+          <t>26宁德时代MTN006B(科创债)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9904,19 +9932,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>032680494.IB</t>
+          <t>102683377.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2.3</v>
+        <v>12.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2.3</v>
+        <v>12.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -9924,44 +9952,44 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>44.95</v>
+        <v>15.16</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26兴化城投PPN006</t>
+          <t>26宁德时代MTN005B(科创债)</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>1.97Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7283</t>
+          <t>1.8059</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.8000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司</t>
+          <t>宁德时代新能源科技股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 15.14</t>
+          <t>C+ 31.05</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9985,49 +10013,49 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>3.7</v>
+        <v>2.2917</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>福建省-宁德市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额2.3亿元,拟用于偿还发行人有息债务[26兴化城投SCP001]</t>
+          <t>本次绿色科技创新债券拟发行规模上限为100亿元,募集资金中97亿元拟用于发行人及下属锂离子电池生产项目的日常运营,以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等;3亿元拟用于置换发行人前三个月内新型动力电池、储能电池研发项目费用支出</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司,华夏银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
@@ -10037,24 +10065,20 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>兴化市城市建设投资有限公司2026年度第八期定向债务融资工具</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第六期绿色科技创新债券(品种二)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2028-08-27</t>
-        </is>
-      </c>
-      <c r="AK43" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -10077,27 +10101,27 @@
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>农产品加工</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10130,7 +10154,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN006B(科创债)</t>
+          <t>26武夷投资MTN004</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10140,7 +10164,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>102683377.IB</t>
+          <t>102683402.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -10149,55 +10173,55 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>15.16</v>
+        <v>61.16</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN005B(科创债)</t>
+          <t>26武夷投资MTN003</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.87Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8059</t>
+          <t>2.0449</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0500/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
+          <t>南平武夷新区投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>B- 36.71</t>
+          <t>C- 22.87</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10207,7 +10231,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-26 09:00</t>
+          <t>08-26 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10221,38 +10245,38 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>2.2917</v>
+        <v>4.84</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>福建省-南平市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本次绿色科技创新债券拟发行规模上限为100亿元,募集资金中97亿元拟用于发行人及下属锂离子电池生产项目的日常运营,以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等;3亿元拟用于置换发行人前三个月内新型动力电池、储能电池研发项目费用支出</t>
+          <t>本期中期票据发行金额为5亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金。[23武夷投资PPN002]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司,华夏银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -10263,7 +10287,7 @@
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -10273,7 +10297,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第六期绿色科技创新债券(品种二)</t>
+          <t>南平武夷新区投资开发集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10304,32 +10328,32 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>电源设备</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10362,7 +10386,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26武夷投资MTN004</t>
+          <t>26中建六局MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10372,49 +10396,49 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102683402.IB</t>
+          <t>102683373.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>61.16</v>
+        <v>50.61</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26武夷投资MTN003</t>
+          <t>23中建六局MTN003(科创票据)</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4.87Y</t>
+          <t>93D+N</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2.0449</t>
+          <t>1.6195</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10424,12 +10448,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>南平武夷新区投资开发集团有限公司</t>
+          <t>中国建筑第六工程局有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 23.70</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10439,7 +10463,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-26 15:00</t>
+          <t>08-26 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10453,38 +10477,42 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>4.84</v>
+        <v>3.39</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z45" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>福建省-南平市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为5亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金。[23武夷投资PPN002]</t>
+          <t>本次中期票据注册金额为人民币21亿元，本期发行金额为人民币7亿元，募集资金拟用于偿还发行人本部存量债务。23 中建六局MTN001(科创票据)</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,兴业证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10495,7 +10523,7 @@
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10505,7 +10533,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>南平武夷新区投资开发集团有限公司2026年度第四期中期票据</t>
+          <t>中国建筑第六工程局有限公司2026年度第一期中期票据(可持续挂钩)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10515,7 +10543,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10536,32 +10564,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10576,12 +10604,12 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY45" s="3" t="inlineStr">
@@ -10594,7 +10622,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26中建六局MTN001(可持续挂钩)</t>
+          <t>26冀中能源MTN017B</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10604,7 +10632,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>102683373.IB</t>
+          <t>102683375.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -10613,55 +10641,55 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>2.10 ~ 2.70</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>50.61</v>
+        <v>103.61</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>23中建六局MTN003(科创票据)</t>
+          <t>26冀中能源MTN015B</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>93D+N</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6195</t>
+          <t>2.3267</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3400/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司</t>
+          <t>冀中能源集团有限责任公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.35</t>
+          <t>C 28.94</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10671,7 +10699,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>08-26 09:00</t>
+          <t>08-26 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10685,17 +10713,17 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>3.39</v>
+        <v>2.26</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.63%~2.73%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10703,24 +10731,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>河北省-邢台市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册金额为人民币21亿元，本期发行金额为人民币7亿元，募集资金拟用于偿还发行人本部存量债务。23 中建六局MTN001(科创票据)</t>
+          <t>本期债务融资工具基础发行金额0亿元，发行金额上限为人民币8亿元，募集资金在扣除发行费用后，拟用于偿还发行人的有息债务。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
@@ -10731,7 +10755,7 @@
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10741,7 +10765,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司2026年度第一期中期票据(可持续挂钩)</t>
+          <t>冀中能源集团有限责任公司2026年度第十七期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10777,27 +10801,27 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10817,7 +10841,7 @@
       </c>
       <c r="AX46" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY46" s="3" t="inlineStr">
@@ -10830,59 +10854,59 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26冀中能源MTN017B</t>
+          <t>26水发02</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-26 19:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>102683375.IB</t>
+          <t>283824.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2.10 ~ 2.70</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>103.61</v>
+        <v>72.16</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26冀中能源MTN015B</t>
+          <t>26水发01</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>2.67Y+2.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2.3267</t>
+          <t>2.1520</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -10892,12 +10916,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>冀中能源集团有限责任公司</t>
+          <t>水发集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.39</t>
+          <t>C 29.86</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10921,19 +10945,15 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.26</v>
+        <v>3.22</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X47" s="3" t="inlineStr">
-        <is>
-          <t>2.63%~2.73%</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X47" s="3"/>
       <c r="Y47" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10942,23 +10962,23 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>河北省-邢台市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额0亿元，发行金额上限为人民币8亿元，募集资金在扣除发行费用后，拟用于偿还发行人的有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[21水发02]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>长江证券股份有限公司,兴业证券股份有限公司,广发证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -10968,28 +10988,28 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>冀中能源集团有限责任公司2026年度第十七期中期票据(品种二)</t>
+          <t>水发集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
@@ -11004,37 +11024,37 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AV47" s="3" t="inlineStr">
@@ -11044,7 +11064,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -11579,7 +11599,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B- 43.96</t>
+          <t>B- 42.19</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11817,7 +11837,7 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C 29.69</t>
+          <t>C 29.78</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -12053,7 +12073,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12283,7 +12303,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>B- 38.62</t>
+          <t>B- 35.61</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12500,7 +12520,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.8453</t>
+          <t>1.8488</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -12515,7 +12535,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>D 4.00</t>
+          <t>D+ 9.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12967,7 +12987,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7800</t>
+          <t>--/1.7800</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -13211,7 +13231,7 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B- 36.11</t>
+          <t>C+ 34.21</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13445,7 +13465,7 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>B 50.97</t>
+          <t>B- 47.37</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13663,7 +13683,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/1.6400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -13673,7 +13693,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 22.86</t>
+          <t>C- 19.00</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -15019,7 +15039,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8500/1.8325</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -15029,7 +15049,7 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>S- 88.62</t>
+          <t>S- 88.57</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15263,7 +15283,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C- 11.79</t>
+          <t>C- 12.24</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15287,7 +15307,7 @@
         </is>
       </c>
       <c r="U66" s="4" t="n">
-        <v>4.82</v>
+        <v>4.8167</v>
       </c>
       <c r="V66" s="4" t="n">
         <v>3.5</v>
@@ -15497,7 +15517,7 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>C- 14.52</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15721,7 +15741,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.7400</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -15731,7 +15751,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>C 28.18</t>
+          <t>C 25.01</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15951,7 +15971,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
@@ -15961,7 +15981,7 @@
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C- 21.99</t>
+          <t>C- 21.22</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16173,7 +16193,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -16183,7 +16203,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C- 21.99</t>
+          <t>C- 21.22</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16415,7 +16435,7 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16647,7 +16667,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -16657,7 +16677,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>B- 36.71</t>
+          <t>C+ 31.05</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16879,7 +16899,7 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7000</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -16889,7 +16909,7 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>B- 39.14</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17123,7 +17143,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B- 39.04</t>
+          <t>C 29.98</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17357,7 +17377,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3400/2.3200</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
@@ -17367,7 +17387,7 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>A- 62.08</t>
+          <t>B- 48.93</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17601,7 +17621,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C 29.84</t>
+          <t>C- 24.81</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17831,7 +17851,7 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>B- 36.50</t>
+          <t>C 29.20</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18059,7 +18079,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0650/2.0600</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -18069,7 +18089,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>B 50.97</t>
+          <t>B- 47.37</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18303,7 +18323,7 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C- 11.74</t>
+          <t>C- 10.38</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18527,7 +18547,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.8100</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -18537,7 +18557,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C 25.57</t>
+          <t>C- 22.29</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18761,7 +18781,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.7600</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -18771,7 +18791,7 @@
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C- 20.71</t>
+          <t>C- 19.83</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18993,7 +19013,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1400/--</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -19003,7 +19023,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>A- 62.08</t>
+          <t>B- 48.93</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19227,7 +19247,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -19237,7 +19257,7 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>B 51.09</t>
+          <t>B- 49.10</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19461,7 +19481,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -19471,7 +19491,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>B- 48.78</t>
+          <t>B- 46.05</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19693,7 +19713,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0800/--</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -19703,7 +19723,7 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 21.93</t>
+          <t>C- 21.26</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19935,7 +19955,11 @@
           <t>上海合晶硅材料股份有限公司</t>
         </is>
       </c>
-      <c r="P86" s="3"/>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -20161,7 +20185,7 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 14.40</t>
+          <t>C- 11.08</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20383,7 +20407,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/1.7000</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -20393,7 +20417,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>B- 45.40</t>
+          <t>B- 42.25</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20615,7 +20639,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7000</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -20625,7 +20649,7 @@
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>B- 39.14</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20849,7 +20873,7 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/1.5300</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -20859,7 +20883,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.76</t>
+          <t>C+ 33.72</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21079,7 +21103,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0500/2.0400</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -21089,7 +21113,7 @@
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -21307,7 +21331,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0500/2.0200</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -21317,7 +21341,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>C- 24.27</t>
+          <t>C- 24.57</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21549,7 +21573,7 @@
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>C- 24.27</t>
+          <t>C- 24.57</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21781,7 +21805,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>C 27.91</t>
+          <t>C 27.03</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -22009,7 +22033,7 @@
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>B- 38.37</t>
+          <t>B- 38.35</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22241,7 +22265,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>A+ 81.65</t>
+          <t>A+ 80.98</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22467,7 +22491,7 @@
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>C 25.67</t>
+          <t>C- 24.27</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-26.xlsx
+++ b/data/credit_bond_all_2026-08-26.xlsx
@@ -951,8 +951,12 @@
           <t>2.70 ~ 2.90</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>158.41</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.70</t>
@@ -1005,7 +1009,9 @@
         </is>
       </c>
       <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="V4" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>7-</t>
@@ -11111,8 +11117,12 @@
           <t>1.60 ~ 2.30</t>
         </is>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="H48" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>41.85</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -11168,8 +11178,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
+      <c r="U48" s="4" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -11303,9 +11317,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ48" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ48" s="3"/>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
@@ -12269,8 +12281,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="H53" s="4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>93.36</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
           <t>2.35</t>
@@ -12326,7 +12342,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U53" s="3"/>
+      <c r="U53" s="4" t="n">
+        <v>3.07</v>
+      </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
@@ -12465,9 +12483,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ53" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ53" s="3"/>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
@@ -12963,8 +12979,12 @@
           <t>1.30 ~ 1.90</t>
         </is>
       </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="H56" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>23.41</v>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -13020,7 +13040,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U56" s="3"/>
+      <c r="U56" s="4" t="n">
+        <v>2.41</v>
+      </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
@@ -13659,8 +13681,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="H59" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>27.49</v>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -13716,8 +13742,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
+      <c r="U59" s="4" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -13851,9 +13881,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ59" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ59" s="3"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
